--- a/grupos/5ALCM - Estadisticos 20211.xlsx
+++ b/grupos/5ALCM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="151">
   <si>
     <t>Materia</t>
   </si>
@@ -194,15 +194,15 @@
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
+    <t>Ortega Valle Manuel</t>
+  </si>
+  <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
     <t>Molina Quezada Raúl</t>
   </si>
   <si>
-    <t>Ortega Valle Manuel</t>
-  </si>
-  <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -218,220 +218,220 @@
     <t>COUDER</t>
   </si>
   <si>
+    <t>ELIZALDE</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MIXCOAC</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>YULIANA</t>
+  </si>
+  <si>
+    <t>ADRIANA ISABEL</t>
+  </si>
+  <si>
+    <t>FRANCISCO EMMANUEL</t>
+  </si>
+  <si>
+    <t>CINTHIA</t>
+  </si>
+  <si>
+    <t>ELYDEN JULYSSA</t>
+  </si>
+  <si>
+    <t>KAROL</t>
+  </si>
+  <si>
+    <t>MARLENE</t>
+  </si>
+  <si>
+    <t>AYOCTLE</t>
+  </si>
+  <si>
+    <t>BALDERAS</t>
+  </si>
+  <si>
+    <t>BONOLA</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
     <t>CABRERA</t>
   </si>
   <si>
-    <t>ELIZALDE</t>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>HUERTA</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MIXCOAC</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>OLTEHUA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>TEHUINTLE</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>SIERRA</t>
+  </si>
+  <si>
+    <t>NUBE</t>
+  </si>
+  <si>
+    <t>BERUDEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>SILVERIO</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>TETLA</t>
   </si>
   <si>
     <t>OFICIAL</t>
   </si>
   <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>YULIANA</t>
+    <t>NIEVES</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>ONOFRE</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>YOPIHUA</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>CARTEÑO</t>
+  </si>
+  <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>LUIS ALEJANDRO</t>
+  </si>
+  <si>
+    <t>IAN ISSAID</t>
+  </si>
+  <si>
+    <t>EMMA NOHEMI</t>
+  </si>
+  <si>
+    <t>MAYTE DOLORES</t>
+  </si>
+  <si>
+    <t>MICHELL</t>
   </si>
   <si>
     <t>AYELEN</t>
   </si>
   <si>
-    <t>ADRIANA ISABEL</t>
+    <t>KARIME GUADALUPE</t>
+  </si>
+  <si>
+    <t>MICAELA</t>
+  </si>
+  <si>
+    <t>MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>JUAN CARLOS</t>
+  </si>
+  <si>
+    <t>MARIANA JOSELIN</t>
+  </si>
+  <si>
+    <t>JESE YAEL</t>
   </si>
   <si>
     <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>FRANCISCO EMMANUEL</t>
-  </si>
-  <si>
-    <t>CINTHIA</t>
-  </si>
-  <si>
-    <t>ELYDEN JULYSSA</t>
-  </si>
-  <si>
-    <t>KAROL</t>
-  </si>
-  <si>
-    <t>MARLENE</t>
-  </si>
-  <si>
-    <t>AYOCTLE</t>
-  </si>
-  <si>
-    <t>BALDERAS</t>
-  </si>
-  <si>
-    <t>BONOLA</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>OLTEHUA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>TEHUINTLE</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>SIERRA</t>
-  </si>
-  <si>
-    <t>NUBE</t>
-  </si>
-  <si>
-    <t>BERUDEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>SILVERIO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>ONOFRE</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>YOPIHUA</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>CARTEÑO</t>
-  </si>
-  <si>
-    <t>KARLA</t>
-  </si>
-  <si>
-    <t>LUIS ALEJANDRO</t>
-  </si>
-  <si>
-    <t>IAN ISSAID</t>
-  </si>
-  <si>
-    <t>EMMA NOHEMI</t>
-  </si>
-  <si>
-    <t>MAYTE DOLORES</t>
-  </si>
-  <si>
-    <t>MICHELL</t>
-  </si>
-  <si>
-    <t>KARIME GUADALUPE</t>
-  </si>
-  <si>
-    <t>MICAELA</t>
-  </si>
-  <si>
-    <t>MARCO ANTONIO</t>
-  </si>
-  <si>
-    <t>JUAN CARLOS</t>
-  </si>
-  <si>
-    <t>MARIANA JOSELIN</t>
-  </si>
-  <si>
-    <t>JESE YAEL</t>
   </si>
   <si>
     <t>JUAN MANUEL</t>
@@ -974,13 +974,13 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
         <v>-1</v>
@@ -989,7 +989,7 @@
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1051,13 +1051,13 @@
         <v>10</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K5">
         <v>-1</v>
@@ -1066,7 +1066,7 @@
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1128,13 +1128,13 @@
         <v>7</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K6">
         <v>-1</v>
@@ -1143,7 +1143,7 @@
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1167,10 +1167,10 @@
         <v>10</v>
       </c>
       <c r="U6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>9</v>
@@ -1179,7 +1179,7 @@
         <v>9</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1193,7 +1193,7 @@
         <v>10</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E7">
         <v>5</v>
@@ -1205,13 +1205,13 @@
         <v>9</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
         <v>-1</v>
@@ -1220,7 +1220,7 @@
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1247,7 +1247,7 @@
         <v>10</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W7">
         <v>5</v>
@@ -1256,7 +1256,7 @@
         <v>8</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1282,13 +1282,13 @@
         <v>10</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
         <v>-1</v>
@@ -1297,7 +1297,7 @@
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1324,7 +1324,7 @@
         <v>10</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -1359,13 +1359,13 @@
         <v>10</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
         <v>-1</v>
@@ -1374,7 +1374,7 @@
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1401,7 +1401,7 @@
         <v>10</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W9">
         <v>10</v>
@@ -1436,13 +1436,13 @@
         <v>9</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K10">
         <v>-1</v>
@@ -1451,7 +1451,7 @@
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1472,13 +1472,13 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W10">
         <v>7</v>
@@ -1487,7 +1487,7 @@
         <v>-1</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1513,13 +1513,13 @@
         <v>10</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
         <v>-1</v>
@@ -1528,7 +1528,7 @@
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1555,7 +1555,7 @@
         <v>10</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>9</v>
@@ -1578,7 +1578,7 @@
         <v>-1</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E12">
         <v>5</v>
@@ -1590,13 +1590,13 @@
         <v>8</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I12">
         <v>-1</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K12">
         <v>-1</v>
@@ -1605,7 +1605,7 @@
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1632,7 +1632,7 @@
         <v>-1</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W12">
         <v>5</v>
@@ -1641,7 +1641,7 @@
         <v>7</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1667,13 +1667,13 @@
         <v>10</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K13">
         <v>-1</v>
@@ -1682,7 +1682,7 @@
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1706,10 +1706,10 @@
         <v>10</v>
       </c>
       <c r="U13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W13">
         <v>9</v>
@@ -1732,7 +1732,7 @@
         <v>-1</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E14">
         <v>6</v>
@@ -1744,13 +1744,13 @@
         <v>5</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I14">
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K14">
         <v>-1</v>
@@ -1759,7 +1759,7 @@
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1786,7 +1786,7 @@
         <v>-1</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W14">
         <v>6</v>
@@ -1821,13 +1821,13 @@
         <v>10</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K15">
         <v>-1</v>
@@ -1836,7 +1836,7 @@
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1863,7 +1863,7 @@
         <v>10</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W15">
         <v>10</v>
@@ -1898,13 +1898,13 @@
         <v>10</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K16">
         <v>-1</v>
@@ -1913,7 +1913,7 @@
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1940,7 +1940,7 @@
         <v>10</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W16">
         <v>10</v>
@@ -1975,13 +1975,13 @@
         <v>8</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
         <v>-1</v>
@@ -1990,7 +1990,7 @@
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2014,7 +2014,7 @@
         <v>5</v>
       </c>
       <c r="U17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V17">
         <v>8</v>
@@ -2052,13 +2052,13 @@
         <v>10</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K18">
         <v>-1</v>
@@ -2067,7 +2067,7 @@
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2129,13 +2129,13 @@
         <v>6</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K19">
         <v>-1</v>
@@ -2144,7 +2144,7 @@
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2180,7 +2180,7 @@
         <v>9</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2206,13 +2206,13 @@
         <v>9</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K20">
         <v>-1</v>
@@ -2221,7 +2221,7 @@
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2242,13 +2242,13 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U20">
         <v>10</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W20">
         <v>9</v>
@@ -2268,7 +2268,7 @@
         <v>10</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D21">
         <v>8</v>
@@ -2283,13 +2283,13 @@
         <v>10</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
         <v>-1</v>
@@ -2298,7 +2298,7 @@
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2322,10 +2322,10 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>9</v>
@@ -2345,7 +2345,7 @@
         <v>6</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D22">
         <v>8</v>
@@ -2360,13 +2360,13 @@
         <v>9</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
         <v>-1</v>
@@ -2375,7 +2375,7 @@
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2396,10 +2396,10 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V22">
         <v>8</v>
@@ -2411,7 +2411,7 @@
         <v>-1</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2437,13 +2437,13 @@
         <v>7</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K23">
         <v>-1</v>
@@ -2452,7 +2452,7 @@
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2514,13 +2514,13 @@
         <v>10</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K24">
         <v>-1</v>
@@ -2529,7 +2529,7 @@
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2556,7 +2556,7 @@
         <v>10</v>
       </c>
       <c r="V24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W24">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>10</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E25">
         <v>5</v>
@@ -2591,13 +2591,13 @@
         <v>6</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I25">
         <v>-1</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K25">
         <v>-1</v>
@@ -2606,7 +2606,7 @@
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2633,7 +2633,7 @@
         <v>10</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W25">
         <v>5</v>
@@ -2642,7 +2642,7 @@
         <v>-1</v>
       </c>
       <c r="Y25">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2668,13 +2668,13 @@
         <v>10</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
         <v>-1</v>
@@ -2683,7 +2683,7 @@
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2710,7 +2710,7 @@
         <v>10</v>
       </c>
       <c r="V26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W26">
         <v>9</v>
@@ -2719,7 +2719,7 @@
         <v>10</v>
       </c>
       <c r="Y26">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2745,13 +2745,13 @@
         <v>10</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K27">
         <v>-1</v>
@@ -2760,7 +2760,7 @@
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2822,13 +2822,13 @@
         <v>10</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K28">
         <v>-1</v>
@@ -2837,7 +2837,7 @@
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2864,7 +2864,7 @@
         <v>10</v>
       </c>
       <c r="V28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W28">
         <v>9</v>
@@ -2899,13 +2899,13 @@
         <v>10</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I29">
         <v>-1</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
         <v>-1</v>
@@ -2914,7 +2914,7 @@
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2941,7 +2941,7 @@
         <v>10</v>
       </c>
       <c r="V29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W29">
         <v>9</v>
@@ -2976,13 +2976,13 @@
         <v>10</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K30">
         <v>-1</v>
@@ -2991,7 +2991,7 @@
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3018,7 +3018,7 @@
         <v>10</v>
       </c>
       <c r="V30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W30">
         <v>9</v>
@@ -3053,13 +3053,13 @@
         <v>10</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K31">
         <v>-1</v>
@@ -3068,7 +3068,7 @@
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3095,7 +3095,7 @@
         <v>10</v>
       </c>
       <c r="V31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W31">
         <v>9</v>
@@ -3130,13 +3130,13 @@
         <v>10</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K32">
         <v>-1</v>
@@ -3145,7 +3145,7 @@
         <v>-1</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3172,7 +3172,7 @@
         <v>10</v>
       </c>
       <c r="V32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W32">
         <v>10</v>
@@ -3207,13 +3207,13 @@
         <v>10</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K33">
         <v>-1</v>
@@ -3222,7 +3222,7 @@
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3272,7 +3272,7 @@
         <v>-1</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E34">
         <v>5</v>
@@ -3284,13 +3284,13 @@
         <v>4</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I34">
         <v>-1</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K34">
         <v>-1</v>
@@ -3299,7 +3299,7 @@
         <v>-1</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3326,7 +3326,7 @@
         <v>-1</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W34">
         <v>5</v>
@@ -3361,13 +3361,13 @@
         <v>10</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I35">
         <v>-1</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K35">
         <v>-1</v>
@@ -3376,7 +3376,7 @@
         <v>-1</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3397,13 +3397,13 @@
         <v>-1</v>
       </c>
       <c r="T35">
+        <v>9</v>
+      </c>
+      <c r="U35">
+        <v>10</v>
+      </c>
+      <c r="V35">
         <v>7</v>
-      </c>
-      <c r="U35">
-        <v>10</v>
-      </c>
-      <c r="V35">
-        <v>6</v>
       </c>
       <c r="W35">
         <v>9</v>
@@ -3438,13 +3438,13 @@
         <v>9</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K36">
         <v>-1</v>
@@ -3453,7 +3453,7 @@
         <v>-1</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3489,7 +3489,7 @@
         <v>7</v>
       </c>
       <c r="Y36">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3515,13 +3515,13 @@
         <v>10</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K37">
         <v>-1</v>
@@ -3530,7 +3530,7 @@
         <v>-1</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3592,13 +3592,13 @@
         <v>5</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I38">
         <v>-1</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K38">
         <v>-1</v>
@@ -3607,7 +3607,7 @@
         <v>-1</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3720,7 +3720,7 @@
         <v>20</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3763,7 +3763,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>58</v>
@@ -3772,30 +3772,30 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="G4">
+        <v>14.29</v>
+      </c>
+      <c r="H4">
+        <v>7.8</v>
+      </c>
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="F4">
-        <v>82.86</v>
-      </c>
-      <c r="G4">
+      <c r="J4">
         <v>0</v>
-      </c>
-      <c r="H4">
-        <v>10</v>
-      </c>
-      <c r="I4">
-        <v>6</v>
-      </c>
-      <c r="J4">
-        <v>17.14</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>59</v>
@@ -3807,27 +3807,27 @@
         <v>30</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F5">
         <v>85.70999999999999</v>
       </c>
       <c r="G5">
+        <v>14.29</v>
+      </c>
+      <c r="H5">
+        <v>8</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="H5">
-        <v>7.8</v>
-      </c>
-      <c r="I5">
-        <v>5</v>
-      </c>
       <c r="J5">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>60</v>
@@ -3836,25 +3836,25 @@
         <v>35</v>
       </c>
       <c r="D6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>85.70999999999999</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="G6">
-        <v>14.29</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>9.9</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3868,19 +3868,19 @@
         <v>35</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>91.43000000000001</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="G7">
-        <v>8.57</v>
+        <v>11.43</v>
       </c>
       <c r="H7">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3896,7 +3896,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3931,10 +3931,10 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920151</v>
+        <v>19330051920157</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3968,133 +3968,133 @@
         <v>19330051920157</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920157</v>
+        <v>19330051920155</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920157</v>
+        <v>19330051920163</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920162</v>
+        <v>19330051920168</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920155</v>
+        <v>19330051920181</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920155</v>
+        <v>19330051920181</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D9" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>19330051920163</v>
+        <v>19330051920183</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D10" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -4105,162 +4105,22 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>19330051920163</v>
+        <v>19330051920183</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>19330051920168</v>
-      </c>
-      <c r="B12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C12" t="s">
-        <v>69</v>
-      </c>
-      <c r="D12" t="s">
-        <v>87</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>19330051920168</v>
-      </c>
-      <c r="B13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" t="s">
-        <v>69</v>
-      </c>
-      <c r="D13" t="s">
-        <v>87</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>19330051920181</v>
-      </c>
-      <c r="B14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" t="s">
-        <v>79</v>
-      </c>
-      <c r="D14" t="s">
-        <v>88</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>19330051920181</v>
-      </c>
-      <c r="B15" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" t="s">
-        <v>79</v>
-      </c>
-      <c r="D15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>19330051920181</v>
-      </c>
-      <c r="B16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D16" t="s">
-        <v>88</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>19330051920183</v>
-      </c>
-      <c r="B17" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17" t="s">
-        <v>80</v>
-      </c>
-      <c r="D17" t="s">
-        <v>89</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>19330051920183</v>
-      </c>
-      <c r="B18" t="s">
-        <v>73</v>
-      </c>
-      <c r="C18" t="s">
-        <v>80</v>
-      </c>
-      <c r="D18" t="s">
-        <v>89</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -4299,16 +4159,16 @@
         <v>19330051920157</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4316,30 +4176,30 @@
         <v>19330051920181</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920155</v>
+        <v>19330051920183</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -4347,64 +4207,64 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920163</v>
+        <v>19330051920276</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920168</v>
+        <v>19330051920155</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920183</v>
+        <v>19330051920163</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" t="s">
         <v>80</v>
       </c>
-      <c r="D7" t="s">
-        <v>89</v>
-      </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920276</v>
+        <v>19330051920168</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D8" t="s">
         <v>81</v>
@@ -4415,47 +4275,47 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920151</v>
+        <v>19330051920148</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="C9" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920162</v>
+        <v>19330051920149</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="C10" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="D10" t="s">
-        <v>84</v>
+        <v>125</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920148</v>
+        <v>19330051920150</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D11" t="s">
         <v>126</v>
@@ -4466,13 +4326,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920149</v>
+        <v>19330051920153</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D12" t="s">
         <v>127</v>
@@ -4483,13 +4343,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920150</v>
+        <v>19330051920152</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D13" t="s">
         <v>128</v>
@@ -4500,13 +4360,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920153</v>
+        <v>19330051920154</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D14" t="s">
         <v>129</v>
@@ -4517,13 +4377,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920152</v>
+        <v>19330051920151</v>
       </c>
       <c r="B15" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C15" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="D15" t="s">
         <v>130</v>
@@ -4534,13 +4394,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920154</v>
+        <v>19330051920160</v>
       </c>
       <c r="B16" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D16" t="s">
         <v>131</v>
@@ -4551,13 +4411,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920160</v>
+        <v>19330051920158</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D17" t="s">
         <v>132</v>
@@ -4568,13 +4428,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920158</v>
+        <v>19330051920159</v>
       </c>
       <c r="B18" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C18" t="s">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="D18" t="s">
         <v>133</v>
@@ -4585,13 +4445,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920159</v>
+        <v>19330051920423</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="C19" t="s">
-        <v>73</v>
+        <v>112</v>
       </c>
       <c r="D19" t="s">
         <v>134</v>
@@ -4602,13 +4462,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920423</v>
+        <v>19330051920281</v>
       </c>
       <c r="B20" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C20" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="D20" t="s">
         <v>135</v>
@@ -4619,13 +4479,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920281</v>
+        <v>19330051920161</v>
       </c>
       <c r="B21" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C21" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="D21" t="s">
         <v>136</v>
@@ -4636,13 +4496,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920161</v>
+        <v>19330051920162</v>
       </c>
       <c r="B22" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C22" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D22" t="s">
         <v>137</v>
@@ -4656,10 +4516,10 @@
         <v>19330051920156</v>
       </c>
       <c r="B23" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C23" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D23" t="s">
         <v>138</v>
@@ -4673,10 +4533,10 @@
         <v>19330051920165</v>
       </c>
       <c r="B24" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C24" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D24" t="s">
         <v>139</v>
@@ -4690,13 +4550,13 @@
         <v>19330051920166</v>
       </c>
       <c r="B25" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C25" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D25" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -4707,10 +4567,10 @@
         <v>19330051920170</v>
       </c>
       <c r="B26" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C26" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D26" t="s">
         <v>140</v>
@@ -4724,10 +4584,10 @@
         <v>19330051920172</v>
       </c>
       <c r="B27" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C27" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D27" t="s">
         <v>141</v>
@@ -4741,10 +4601,10 @@
         <v>19330051920173</v>
       </c>
       <c r="B28" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C28" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D28" t="s">
         <v>142</v>
@@ -4758,10 +4618,10 @@
         <v>19330051920176</v>
       </c>
       <c r="B29" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C29" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D29" t="s">
         <v>143</v>
@@ -4775,10 +4635,10 @@
         <v>19330051920174</v>
       </c>
       <c r="B30" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D30" t="s">
         <v>144</v>
@@ -4792,10 +4652,10 @@
         <v>19330051920175</v>
       </c>
       <c r="B31" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C31" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D31" t="s">
         <v>145</v>
@@ -4809,10 +4669,10 @@
         <v>19330051920178</v>
       </c>
       <c r="B32" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C32" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D32" t="s">
         <v>146</v>
@@ -4826,10 +4686,10 @@
         <v>19330051920179</v>
       </c>
       <c r="B33" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C33" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="D33" t="s">
         <v>147</v>
@@ -4843,10 +4703,10 @@
         <v>19330051920180</v>
       </c>
       <c r="B34" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C34" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D34" t="s">
         <v>148</v>
@@ -4860,10 +4720,10 @@
         <v>19330051920303</v>
       </c>
       <c r="B35" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C35" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D35" t="s">
         <v>149</v>
@@ -4877,10 +4737,10 @@
         <v>19330051920182</v>
       </c>
       <c r="B36" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C36" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D36" t="s">
         <v>150</v>
@@ -4896,7 +4756,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4931,22 +4791,22 @@
         <v>19330051920151</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>130</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4954,19 +4814,19 @@
         <v>19330051920151</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>130</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4974,22 +4834,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920163</v>
+        <v>19330051920276</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -4997,39 +4857,39 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920163</v>
+        <v>19330051920159</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>133</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920276</v>
+        <v>19330051920163</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -5043,16 +4903,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920159</v>
+        <v>19330051920165</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>115</v>
       </c>
       <c r="D7" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E7" t="s">
         <v>5</v>
@@ -5061,52 +4921,6 @@
         <v>56</v>
       </c>
       <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>19330051920162</v>
-      </c>
-      <c r="B8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D8" t="s">
-        <v>84</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>19330051920165</v>
-      </c>
-      <c r="B9" t="s">
-        <v>100</v>
-      </c>
-      <c r="C9" t="s">
-        <v>117</v>
-      </c>
-      <c r="D9" t="s">
-        <v>139</v>
-      </c>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" t="s">
-        <v>56</v>
-      </c>
-      <c r="G9">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ALCM - Estadisticos 20211.xlsx
+++ b/grupos/5ALCM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="151">
   <si>
     <t>Materia</t>
   </si>
@@ -191,15 +191,15 @@
     <t>Ángel Martínez Gerson Hermenegildo</t>
   </si>
   <si>
+    <t>Ortega Valle Manuel</t>
+  </si>
+  <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
-    <t>Ortega Valle Manuel</t>
-  </si>
-  <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
     <t>Molina Quezada Raúl</t>
   </si>
   <si>
@@ -215,223 +215,223 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ELIZALDE</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MIXCOAC</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>ADRIANA ISABEL</t>
+  </si>
+  <si>
+    <t>FRANCISCO EMMANUEL</t>
+  </si>
+  <si>
+    <t>ELYDEN JULYSSA</t>
+  </si>
+  <si>
+    <t>KAROL</t>
+  </si>
+  <si>
+    <t>MARLENE</t>
+  </si>
+  <si>
+    <t>AYOCTLE</t>
+  </si>
+  <si>
+    <t>BALDERAS</t>
+  </si>
+  <si>
+    <t>BONOLA</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
     <t>COUDER</t>
   </si>
   <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>MIXCOAC</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>OLTEHUA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
+    <t>TEHUINTLE</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>SIERRA</t>
+  </si>
+  <si>
+    <t>NUBE</t>
+  </si>
+  <si>
+    <t>BERUDEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>SILVERIO</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>NIEVES</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>ONOFRE</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>YOPIHUA</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>CARTEÑO</t>
+  </si>
+  <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>LUIS ALEJANDRO</t>
+  </si>
+  <si>
+    <t>IAN ISSAID</t>
+  </si>
+  <si>
+    <t>EMMA NOHEMI</t>
+  </si>
+  <si>
+    <t>MAYTE DOLORES</t>
+  </si>
+  <si>
+    <t>MICHELL</t>
   </si>
   <si>
     <t>YULIANA</t>
   </si>
   <si>
-    <t>ADRIANA ISABEL</t>
-  </si>
-  <si>
-    <t>FRANCISCO EMMANUEL</t>
+    <t>AYELEN</t>
+  </si>
+  <si>
+    <t>KARIME GUADALUPE</t>
+  </si>
+  <si>
+    <t>MICAELA</t>
+  </si>
+  <si>
+    <t>MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>JUAN CARLOS</t>
+  </si>
+  <si>
+    <t>MARIANA JOSELIN</t>
+  </si>
+  <si>
+    <t>JESE YAEL</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
   </si>
   <si>
     <t>CINTHIA</t>
-  </si>
-  <si>
-    <t>ELYDEN JULYSSA</t>
-  </si>
-  <si>
-    <t>KAROL</t>
-  </si>
-  <si>
-    <t>MARLENE</t>
-  </si>
-  <si>
-    <t>AYOCTLE</t>
-  </si>
-  <si>
-    <t>BALDERAS</t>
-  </si>
-  <si>
-    <t>BONOLA</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>OLTEHUA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>TEHUINTLE</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>SIERRA</t>
-  </si>
-  <si>
-    <t>NUBE</t>
-  </si>
-  <si>
-    <t>BERUDEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>SILVERIO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>ONOFRE</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>YOPIHUA</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>CARTEÑO</t>
-  </si>
-  <si>
-    <t>KARLA</t>
-  </si>
-  <si>
-    <t>LUIS ALEJANDRO</t>
-  </si>
-  <si>
-    <t>IAN ISSAID</t>
-  </si>
-  <si>
-    <t>EMMA NOHEMI</t>
-  </si>
-  <si>
-    <t>MAYTE DOLORES</t>
-  </si>
-  <si>
-    <t>MICHELL</t>
-  </si>
-  <si>
-    <t>AYELEN</t>
-  </si>
-  <si>
-    <t>KARIME GUADALUPE</t>
-  </si>
-  <si>
-    <t>MICAELA</t>
-  </si>
-  <si>
-    <t>MARCO ANTONIO</t>
-  </si>
-  <si>
-    <t>JUAN CARLOS</t>
-  </si>
-  <si>
-    <t>MARIANA JOSELIN</t>
-  </si>
-  <si>
-    <t>JESE YAEL</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
   </si>
   <si>
     <t>JUAN MANUEL</t>
@@ -986,7 +986,7 @@
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
         <v>10</v>
@@ -1063,7 +1063,7 @@
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
         <v>10</v>
@@ -1099,7 +1099,7 @@
         <v>8</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y5">
         <v>10</v>
@@ -1140,7 +1140,7 @@
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
         <v>9</v>
@@ -1176,7 +1176,7 @@
         <v>9</v>
       </c>
       <c r="X6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y6">
         <v>8</v>
@@ -1217,7 +1217,7 @@
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M7">
         <v>7</v>
@@ -1294,7 +1294,7 @@
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
         <v>10</v>
@@ -1371,7 +1371,7 @@
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
         <v>10</v>
@@ -1430,7 +1430,7 @@
         <v>7</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G10">
         <v>9</v>
@@ -1448,7 +1448,7 @@
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
         <v>10</v>
@@ -1484,7 +1484,7 @@
         <v>7</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y10">
         <v>10</v>
@@ -1525,7 +1525,7 @@
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
         <v>10</v>
@@ -1679,7 +1679,7 @@
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
         <v>10</v>
@@ -1833,7 +1833,7 @@
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
         <v>10</v>
@@ -1910,7 +1910,7 @@
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
         <v>10</v>
@@ -1987,7 +1987,7 @@
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
         <v>7</v>
@@ -2023,7 +2023,7 @@
         <v>7</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y17">
         <v>8</v>
@@ -2064,7 +2064,7 @@
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
         <v>10</v>
@@ -2209,7 +2209,7 @@
         <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J20">
         <v>8</v>
@@ -2218,7 +2218,7 @@
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
         <v>9</v>
@@ -2245,7 +2245,7 @@
         <v>10</v>
       </c>
       <c r="U20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V20">
         <v>8</v>
@@ -2295,7 +2295,7 @@
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M21">
         <v>10</v>
@@ -2331,7 +2331,7 @@
         <v>9</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>10</v>
@@ -2354,7 +2354,7 @@
         <v>6</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G22">
         <v>9</v>
@@ -2372,7 +2372,7 @@
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
         <v>7</v>
@@ -2408,7 +2408,7 @@
         <v>6</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y22">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
         <v>7</v>
@@ -2485,7 +2485,7 @@
         <v>7</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y23">
         <v>7</v>
@@ -2526,7 +2526,7 @@
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
         <v>10</v>
@@ -2680,7 +2680,7 @@
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
         <v>8</v>
@@ -2757,7 +2757,7 @@
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
         <v>10</v>
@@ -2834,7 +2834,7 @@
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
         <v>10</v>
@@ -2911,7 +2911,7 @@
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
         <v>10</v>
@@ -2988,7 +2988,7 @@
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
         <v>10</v>
@@ -3065,7 +3065,7 @@
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
         <v>10</v>
@@ -3142,7 +3142,7 @@
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M32">
         <v>10</v>
@@ -3219,7 +3219,7 @@
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
         <v>10</v>
@@ -3373,7 +3373,7 @@
         <v>-1</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M35">
         <v>10</v>
@@ -3409,7 +3409,7 @@
         <v>9</v>
       </c>
       <c r="X35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y35">
         <v>10</v>
@@ -3450,7 +3450,7 @@
         <v>-1</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M36">
         <v>6</v>
@@ -3486,7 +3486,7 @@
         <v>6</v>
       </c>
       <c r="X36">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y36">
         <v>8</v>
@@ -3527,7 +3527,7 @@
         <v>-1</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M37">
         <v>10</v>
@@ -3731,7 +3731,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>57</v>
@@ -3740,30 +3740,30 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E3">
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="G3">
+        <v>14.29</v>
+      </c>
+      <c r="H3">
+        <v>7.8</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="F3">
-        <v>82.86</v>
-      </c>
-      <c r="G3">
+      <c r="J3">
         <v>0</v>
-      </c>
-      <c r="H3">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="I3">
-        <v>6</v>
-      </c>
-      <c r="J3">
-        <v>17.14</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>58</v>
@@ -3784,7 +3784,7 @@
         <v>14.29</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3795,7 +3795,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>59</v>
@@ -3804,25 +3804,25 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>85.70999999999999</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="G5">
-        <v>14.29</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3848,7 +3848,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I6">
         <v>4</v>
@@ -3896,7 +3896,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3925,22 +3925,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>19330051920276</v>
+        <v>19330051920157</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3948,33 +3948,33 @@
         <v>19330051920157</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920157</v>
+        <v>19330051920155</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -3985,27 +3985,27 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920155</v>
+        <v>19330051920168</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920163</v>
+        <v>19330051920181</v>
       </c>
       <c r="B6" t="s">
         <v>68</v>
@@ -4014,112 +4014,72 @@
         <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920168</v>
+        <v>19330051920181</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920181</v>
+        <v>19330051920183</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920181</v>
+        <v>19330051920183</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>19330051920183</v>
-      </c>
-      <c r="B10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" t="s">
-        <v>76</v>
-      </c>
-      <c r="D10" t="s">
-        <v>83</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>19330051920183</v>
-      </c>
-      <c r="B11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" t="s">
-        <v>76</v>
-      </c>
-      <c r="D11" t="s">
-        <v>83</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
         <v>60</v>
       </c>
     </row>
@@ -4159,13 +4119,13 @@
         <v>19330051920157</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -4176,13 +4136,13 @@
         <v>19330051920181</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -4193,13 +4153,13 @@
         <v>19330051920183</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -4207,16 +4167,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920276</v>
+        <v>19330051920155</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -4224,16 +4184,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920155</v>
+        <v>19330051920168</v>
       </c>
       <c r="B6" t="s">
         <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -4241,44 +4201,44 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920163</v>
+        <v>19330051920148</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920168</v>
+        <v>19330051920149</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>123</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920148</v>
+        <v>19330051920150</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
         <v>104</v>
@@ -4292,10 +4252,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920149</v>
+        <v>19330051920153</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
         <v>105</v>
@@ -4309,10 +4269,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920150</v>
+        <v>19330051920152</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
         <v>106</v>
@@ -4326,10 +4286,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920153</v>
+        <v>19330051920154</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
         <v>107</v>
@@ -4343,13 +4303,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920152</v>
+        <v>19330051920276</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D13" t="s">
         <v>128</v>
@@ -4360,13 +4320,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920154</v>
+        <v>19330051920151</v>
       </c>
       <c r="B14" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="D14" t="s">
         <v>129</v>
@@ -4377,13 +4337,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920151</v>
+        <v>19330051920160</v>
       </c>
       <c r="B15" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="D15" t="s">
         <v>130</v>
@@ -4394,13 +4354,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920160</v>
+        <v>19330051920158</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D16" t="s">
         <v>131</v>
@@ -4411,13 +4371,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920158</v>
+        <v>19330051920159</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C17" t="s">
-        <v>111</v>
+        <v>69</v>
       </c>
       <c r="D17" t="s">
         <v>132</v>
@@ -4428,13 +4388,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920159</v>
+        <v>19330051920423</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>71</v>
+        <v>110</v>
       </c>
       <c r="D18" t="s">
         <v>133</v>
@@ -4445,13 +4405,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920423</v>
+        <v>19330051920281</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C19" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="D19" t="s">
         <v>134</v>
@@ -4462,13 +4422,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920281</v>
+        <v>19330051920161</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="D20" t="s">
         <v>135</v>
@@ -4479,13 +4439,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920161</v>
+        <v>19330051920162</v>
       </c>
       <c r="B21" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C21" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D21" t="s">
         <v>136</v>
@@ -4496,13 +4456,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920162</v>
+        <v>19330051920163</v>
       </c>
       <c r="B22" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="D22" t="s">
         <v>137</v>
@@ -4516,10 +4476,10 @@
         <v>19330051920156</v>
       </c>
       <c r="B23" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C23" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="D23" t="s">
         <v>138</v>
@@ -4533,10 +4493,10 @@
         <v>19330051920165</v>
       </c>
       <c r="B24" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D24" t="s">
         <v>139</v>
@@ -4550,13 +4510,13 @@
         <v>19330051920166</v>
       </c>
       <c r="B25" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D25" t="s">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -4567,10 +4527,10 @@
         <v>19330051920170</v>
       </c>
       <c r="B26" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C26" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D26" t="s">
         <v>140</v>
@@ -4584,10 +4544,10 @@
         <v>19330051920172</v>
       </c>
       <c r="B27" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C27" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D27" t="s">
         <v>141</v>
@@ -4601,10 +4561,10 @@
         <v>19330051920173</v>
       </c>
       <c r="B28" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C28" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D28" t="s">
         <v>142</v>
@@ -4618,10 +4578,10 @@
         <v>19330051920176</v>
       </c>
       <c r="B29" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="C29" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D29" t="s">
         <v>143</v>
@@ -4635,10 +4595,10 @@
         <v>19330051920174</v>
       </c>
       <c r="B30" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="C30" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D30" t="s">
         <v>144</v>
@@ -4652,10 +4612,10 @@
         <v>19330051920175</v>
       </c>
       <c r="B31" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="C31" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D31" t="s">
         <v>145</v>
@@ -4669,10 +4629,10 @@
         <v>19330051920178</v>
       </c>
       <c r="B32" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C32" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D32" t="s">
         <v>146</v>
@@ -4686,10 +4646,10 @@
         <v>19330051920179</v>
       </c>
       <c r="B33" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C33" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D33" t="s">
         <v>147</v>
@@ -4703,10 +4663,10 @@
         <v>19330051920180</v>
       </c>
       <c r="B34" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C34" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D34" t="s">
         <v>148</v>
@@ -4720,10 +4680,10 @@
         <v>19330051920303</v>
       </c>
       <c r="B35" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C35" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D35" t="s">
         <v>149</v>
@@ -4737,10 +4697,10 @@
         <v>19330051920182</v>
       </c>
       <c r="B36" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C36" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D36" t="s">
         <v>150</v>
@@ -4756,7 +4716,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4791,19 +4751,19 @@
         <v>19330051920151</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4814,19 +4774,19 @@
         <v>19330051920151</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4834,39 +4794,39 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920276</v>
+        <v>19330051920159</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920159</v>
+        <v>19330051920165</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="D5" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="E5" t="s">
         <v>5</v>
@@ -4875,52 +4835,6 @@
         <v>56</v>
       </c>
       <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>19330051920163</v>
-      </c>
-      <c r="B6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>57</v>
-      </c>
-      <c r="G6">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>19330051920165</v>
-      </c>
-      <c r="B7" t="s">
-        <v>97</v>
-      </c>
-      <c r="C7" t="s">
-        <v>115</v>
-      </c>
-      <c r="D7" t="s">
-        <v>139</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G7">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ALCM - Estadisticos 20211.xlsx
+++ b/grupos/5ALCM - Estadisticos 20211.xlsx
@@ -983,7 +983,7 @@
         <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
         <v>10</v>
@@ -1060,7 +1060,7 @@
         <v>6</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L5">
         <v>10</v>
@@ -1137,7 +1137,7 @@
         <v>8</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>10</v>
@@ -1173,7 +1173,7 @@
         <v>8</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X6">
         <v>10</v>
@@ -1214,7 +1214,7 @@
         <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <v>7</v>
@@ -1291,7 +1291,7 @@
         <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
         <v>10</v>
@@ -1368,7 +1368,7 @@
         <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
         <v>10</v>
@@ -1445,7 +1445,7 @@
         <v>6</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
         <v>10</v>
@@ -1481,7 +1481,7 @@
         <v>7</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>8</v>
@@ -1522,7 +1522,7 @@
         <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
         <v>10</v>
@@ -1599,7 +1599,7 @@
         <v>6</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L12">
         <v>-1</v>
@@ -1676,7 +1676,7 @@
         <v>9</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L13">
         <v>10</v>
@@ -1712,7 +1712,7 @@
         <v>9</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>10</v>
@@ -1753,7 +1753,7 @@
         <v>6</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
         <v>-1</v>
@@ -1830,7 +1830,7 @@
         <v>10</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
         <v>10</v>
@@ -1907,7 +1907,7 @@
         <v>9</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
         <v>10</v>
@@ -1984,7 +1984,7 @@
         <v>8</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
         <v>10</v>
@@ -2061,7 +2061,7 @@
         <v>7</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
         <v>10</v>
@@ -2138,7 +2138,7 @@
         <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L19">
         <v>-1</v>
@@ -2215,7 +2215,7 @@
         <v>8</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
         <v>10</v>
@@ -2292,7 +2292,7 @@
         <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
         <v>9</v>
@@ -2328,7 +2328,7 @@
         <v>9</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>8</v>
@@ -2369,7 +2369,7 @@
         <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
         <v>10</v>
@@ -2405,7 +2405,7 @@
         <v>8</v>
       </c>
       <c r="W22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X22">
         <v>8</v>
@@ -2446,7 +2446,7 @@
         <v>8</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L23">
         <v>10</v>
@@ -2482,7 +2482,7 @@
         <v>8</v>
       </c>
       <c r="W23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X23">
         <v>9</v>
@@ -2523,7 +2523,7 @@
         <v>9</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
         <v>10</v>
@@ -2677,7 +2677,7 @@
         <v>9</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L26">
         <v>9</v>
@@ -2754,7 +2754,7 @@
         <v>9</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
         <v>10</v>
@@ -2831,7 +2831,7 @@
         <v>9</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L28">
         <v>10</v>
@@ -2908,7 +2908,7 @@
         <v>8</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L29">
         <v>10</v>
@@ -2985,7 +2985,7 @@
         <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L30">
         <v>10</v>
@@ -3062,7 +3062,7 @@
         <v>9</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L31">
         <v>10</v>
@@ -3139,7 +3139,7 @@
         <v>9</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L32">
         <v>10</v>
@@ -3175,7 +3175,7 @@
         <v>9</v>
       </c>
       <c r="W32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X32">
         <v>10</v>
@@ -3216,7 +3216,7 @@
         <v>8</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L33">
         <v>10</v>
@@ -3370,7 +3370,7 @@
         <v>7</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L35">
         <v>10</v>
@@ -3447,7 +3447,7 @@
         <v>7</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L36">
         <v>10</v>
@@ -3524,7 +3524,7 @@
         <v>8</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L37">
         <v>10</v>
@@ -3560,7 +3560,7 @@
         <v>8</v>
       </c>
       <c r="W37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X37">
         <v>10</v>

--- a/grupos/5ALCM - Estadisticos 20211.xlsx
+++ b/grupos/5ALCM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="151">
   <si>
     <t>Materia</t>
   </si>
@@ -188,21 +188,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
+    <t>Molina Quezada Raúl</t>
+  </si>
+  <si>
     <t>Ángel Martínez Gerson Hermenegildo</t>
   </si>
   <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
     <t>Ortega Valle Manuel</t>
   </si>
   <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
-    <t>Molina Quezada Raúl</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -215,262 +215,262 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>AYOCTLE</t>
+  </si>
+  <si>
+    <t>BALDERAS</t>
+  </si>
+  <si>
+    <t>BONOLA</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
+    <t>COUDER</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
     <t>ELIZALDE</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
     <t>MIXCOAC</t>
   </si>
   <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>OLTEHUA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TEHUINTLE</t>
+  </si>
+  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
     <t>ZUÑIGA</t>
   </si>
   <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>SIERRA</t>
+  </si>
+  <si>
+    <t>NUBE</t>
+  </si>
+  <si>
+    <t>BERUDEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
     <t>JUAREZ</t>
   </si>
   <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>SILVERIO</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
     <t>RICO</t>
   </si>
   <si>
+    <t>NIEVES</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>ONOFRE</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>YOPIHUA</t>
+  </si>
+  <si>
     <t>PALOMARES</t>
   </si>
   <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>CARTEÑO</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>LUIS ALEJANDRO</t>
+  </si>
+  <si>
+    <t>IAN ISSAID</t>
+  </si>
+  <si>
+    <t>EMMA NOHEMI</t>
+  </si>
+  <si>
+    <t>MAYTE DOLORES</t>
+  </si>
+  <si>
+    <t>MICHELL</t>
+  </si>
+  <si>
+    <t>YULIANA</t>
+  </si>
+  <si>
+    <t>AYELEN</t>
+  </si>
+  <si>
     <t>ADRIANA ISABEL</t>
   </si>
   <si>
+    <t>KARIME GUADALUPE</t>
+  </si>
+  <si>
+    <t>MICAELA</t>
+  </si>
+  <si>
+    <t>MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>JUAN CARLOS</t>
+  </si>
+  <si>
+    <t>MARIANA JOSELIN</t>
+  </si>
+  <si>
+    <t>JESE YAEL</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
     <t>FRANCISCO EMMANUEL</t>
   </si>
   <si>
+    <t>CINTHIA</t>
+  </si>
+  <si>
+    <t>JUAN MANUEL</t>
+  </si>
+  <si>
+    <t>MARTHA</t>
+  </si>
+  <si>
     <t>ELYDEN JULYSSA</t>
   </si>
   <si>
+    <t>DIEGO MIGUEL</t>
+  </si>
+  <si>
+    <t>JAXIRY JAZMIN</t>
+  </si>
+  <si>
+    <t>KATHERINE AZUL</t>
+  </si>
+  <si>
+    <t>ABRIL CITLALLI</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>LIZETH</t>
+  </si>
+  <si>
+    <t>YAMILET</t>
+  </si>
+  <si>
+    <t>DANNA ARLETTE</t>
+  </si>
+  <si>
     <t>KAROL</t>
   </si>
   <si>
+    <t>RUTH</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>ESTEFANIA</t>
+  </si>
+  <si>
     <t>MARLENE</t>
-  </si>
-  <si>
-    <t>AYOCTLE</t>
-  </si>
-  <si>
-    <t>BALDERAS</t>
-  </si>
-  <si>
-    <t>BONOLA</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>COUDER</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>OLTEHUA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TEHUINTLE</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>SIERRA</t>
-  </si>
-  <si>
-    <t>NUBE</t>
-  </si>
-  <si>
-    <t>BERUDEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>SILVERIO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>ONOFRE</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>YOPIHUA</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>CARTEÑO</t>
-  </si>
-  <si>
-    <t>KARLA</t>
-  </si>
-  <si>
-    <t>LUIS ALEJANDRO</t>
-  </si>
-  <si>
-    <t>IAN ISSAID</t>
-  </si>
-  <si>
-    <t>EMMA NOHEMI</t>
-  </si>
-  <si>
-    <t>MAYTE DOLORES</t>
-  </si>
-  <si>
-    <t>MICHELL</t>
-  </si>
-  <si>
-    <t>YULIANA</t>
-  </si>
-  <si>
-    <t>AYELEN</t>
-  </si>
-  <si>
-    <t>KARIME GUADALUPE</t>
-  </si>
-  <si>
-    <t>MICAELA</t>
-  </si>
-  <si>
-    <t>MARCO ANTONIO</t>
-  </si>
-  <si>
-    <t>JUAN CARLOS</t>
-  </si>
-  <si>
-    <t>MARIANA JOSELIN</t>
-  </si>
-  <si>
-    <t>JESE YAEL</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>CINTHIA</t>
-  </si>
-  <si>
-    <t>JUAN MANUEL</t>
-  </si>
-  <si>
-    <t>MARTHA</t>
-  </si>
-  <si>
-    <t>DIEGO MIGUEL</t>
-  </si>
-  <si>
-    <t>JAXIRY JAZMIN</t>
-  </si>
-  <si>
-    <t>KATHERINE AZUL</t>
-  </si>
-  <si>
-    <t>ABRIL CITLALLI</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>LIZETH</t>
-  </si>
-  <si>
-    <t>YAMILET</t>
-  </si>
-  <si>
-    <t>DANNA ARLETTE</t>
-  </si>
-  <si>
-    <t>RUTH</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>ESTEFANIA</t>
   </si>
 </sst>
 </file>
@@ -992,22 +992,22 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -1069,37 +1069,37 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>10</v>
       </c>
       <c r="U5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y5">
         <v>10</v>
@@ -1146,37 +1146,37 @@
         <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U6">
         <v>9</v>
       </c>
       <c r="V6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W6">
         <v>8</v>
       </c>
       <c r="X6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>8</v>
@@ -1208,7 +1208,7 @@
         <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1223,31 +1223,31 @@
         <v>7</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W7">
         <v>5</v>
@@ -1300,22 +1300,22 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>10</v>
@@ -1377,28 +1377,28 @@
         <v>10</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>10</v>
       </c>
       <c r="U9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V9">
         <v>9</v>
@@ -1454,22 +1454,22 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>8</v>
@@ -1481,13 +1481,13 @@
         <v>7</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>8</v>
       </c>
       <c r="Y10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1531,22 +1531,22 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>10</v>
@@ -1555,7 +1555,7 @@
         <v>10</v>
       </c>
       <c r="V11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>9</v>
@@ -1575,7 +1575,7 @@
         <v>5</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D12">
         <v>5</v>
@@ -1593,7 +1593,7 @@
         <v>5</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J12">
         <v>6</v>
@@ -1602,37 +1602,37 @@
         <v>5</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M12">
         <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W12">
         <v>5</v>
@@ -1641,7 +1641,7 @@
         <v>7</v>
       </c>
       <c r="Y12">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1685,22 +1685,22 @@
         <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>10</v>
@@ -1729,7 +1729,7 @@
         <v>5</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D14">
         <v>5</v>
@@ -1738,7 +1738,7 @@
         <v>6</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -1747,7 +1747,7 @@
         <v>5</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J14">
         <v>6</v>
@@ -1756,43 +1756,43 @@
         <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
         <v>5</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T14">
         <v>5</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W14">
         <v>6</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>5</v>
@@ -1839,22 +1839,22 @@
         <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>10</v>
@@ -1916,22 +1916,22 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>10</v>
@@ -1993,28 +1993,28 @@
         <v>7</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V17">
         <v>8</v>
@@ -2070,34 +2070,34 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
         <v>10</v>
       </c>
       <c r="U18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V18">
         <v>7</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>10</v>
@@ -2141,34 +2141,34 @@
         <v>6</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M19">
         <v>8</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
         <v>8</v>
       </c>
       <c r="U19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V19">
         <v>8</v>
@@ -2177,10 +2177,10 @@
         <v>6</v>
       </c>
       <c r="X19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2224,25 +2224,25 @@
         <v>9</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U20">
         <v>9</v>
@@ -2301,28 +2301,28 @@
         <v>10</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>10</v>
       </c>
       <c r="U21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V21">
         <v>9</v>
@@ -2378,28 +2378,28 @@
         <v>7</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T22">
         <v>7</v>
       </c>
       <c r="U22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V22">
         <v>8</v>
@@ -2411,7 +2411,7 @@
         <v>8</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2455,40 +2455,40 @@
         <v>7</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V23">
         <v>8</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X23">
         <v>9</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2532,22 +2532,22 @@
         <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>10</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G25">
         <v>6</v>
@@ -2594,55 +2594,55 @@
         <v>5</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J25">
         <v>6</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M25">
         <v>5</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W25">
         <v>5</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y25">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2686,22 +2686,22 @@
         <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T26">
         <v>10</v>
@@ -2713,7 +2713,7 @@
         <v>9</v>
       </c>
       <c r="W26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>10</v>
@@ -2763,22 +2763,22 @@
         <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>10</v>
@@ -2840,28 +2840,28 @@
         <v>10</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>10</v>
       </c>
       <c r="U28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V28">
         <v>9</v>
@@ -2902,7 +2902,7 @@
         <v>9</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J29">
         <v>8</v>
@@ -2917,40 +2917,40 @@
         <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V29">
         <v>7</v>
       </c>
       <c r="W29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X29">
         <v>10</v>
       </c>
       <c r="Y29">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2994,22 +2994,22 @@
         <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>10</v>
@@ -3018,10 +3018,10 @@
         <v>10</v>
       </c>
       <c r="V30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X30">
         <v>10</v>
@@ -3071,28 +3071,28 @@
         <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
         <v>10</v>
       </c>
       <c r="U31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V31">
         <v>9</v>
@@ -3148,28 +3148,28 @@
         <v>10</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>10</v>
       </c>
       <c r="U32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V32">
         <v>9</v>
@@ -3225,22 +3225,22 @@
         <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>10</v>
@@ -3252,7 +3252,7 @@
         <v>8</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X33">
         <v>10</v>
@@ -3269,7 +3269,7 @@
         <v>4</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D34">
         <v>5</v>
@@ -3278,7 +3278,7 @@
         <v>5</v>
       </c>
       <c r="F34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G34">
         <v>4</v>
@@ -3287,55 +3287,55 @@
         <v>6</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J34">
         <v>6</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M34">
         <v>7</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W34">
         <v>5</v>
       </c>
       <c r="X34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y34">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3364,7 +3364,7 @@
         <v>10</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J35">
         <v>7</v>
@@ -3379,40 +3379,40 @@
         <v>10</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V35">
         <v>7</v>
       </c>
       <c r="W35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X35">
         <v>10</v>
       </c>
       <c r="Y35">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3456,37 +3456,37 @@
         <v>6</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W36">
         <v>6</v>
       </c>
       <c r="X36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y36">
         <v>8</v>
@@ -3533,34 +3533,34 @@
         <v>10</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T37">
         <v>10</v>
       </c>
       <c r="U37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V37">
         <v>8</v>
       </c>
       <c r="W37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X37">
         <v>10</v>
@@ -3577,7 +3577,7 @@
         <v>4</v>
       </c>
       <c r="C38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D38">
         <v>7</v>
@@ -3586,7 +3586,7 @@
         <v>5</v>
       </c>
       <c r="F38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G38">
         <v>5</v>
@@ -3595,52 +3595,52 @@
         <v>5</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J38">
         <v>6</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M38">
         <v>5</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T38">
         <v>5</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W38">
         <v>5</v>
       </c>
       <c r="X38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y38">
         <v>5</v>
@@ -3699,7 +3699,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>56</v>
@@ -3708,19 +3708,19 @@
         <v>35</v>
       </c>
       <c r="D2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>80</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="G2">
-        <v>20</v>
+        <v>14.29</v>
       </c>
       <c r="H2">
-        <v>8.800000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3731,7 +3731,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>57</v>
@@ -3740,19 +3740,19 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>85.70999999999999</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="G3">
-        <v>14.29</v>
+        <v>11.43</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3763,7 +3763,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>58</v>
@@ -3772,19 +3772,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>85.70999999999999</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="G4">
-        <v>14.29</v>
+        <v>5.71</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>8.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3795,92 +3795,92 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C5">
         <v>35</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>88.56999999999999</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>5.71</v>
       </c>
       <c r="H5">
-        <v>9.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>11.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C6">
         <v>35</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>88.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>11.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C7">
         <v>35</v>
       </c>
       <c r="D7">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>88.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>11.43</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>8.800000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3896,7 +3896,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3921,166 +3921,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>19330051920157</v>
-      </c>
-      <c r="B2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>19330051920157</v>
-      </c>
-      <c r="B3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>19330051920155</v>
-      </c>
-      <c r="B4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>19330051920168</v>
-      </c>
-      <c r="B5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>19330051920181</v>
-      </c>
-      <c r="B6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D6" t="s">
-        <v>77</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>19330051920181</v>
-      </c>
-      <c r="B7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" t="s">
-        <v>77</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>19330051920183</v>
-      </c>
-      <c r="B8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" t="s">
-        <v>73</v>
-      </c>
-      <c r="D8" t="s">
-        <v>78</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>19330051920183</v>
-      </c>
-      <c r="B9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" t="s">
-        <v>73</v>
-      </c>
-      <c r="D9" t="s">
-        <v>78</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -4116,98 +3956,98 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920157</v>
+        <v>19330051920148</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>117</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920181</v>
+        <v>19330051920149</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920183</v>
+        <v>19330051920150</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920155</v>
+        <v>19330051920153</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920168</v>
+        <v>19330051920152</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920148</v>
+        <v>19330051920154</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D7" t="s">
         <v>122</v>
@@ -4218,13 +4058,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920149</v>
+        <v>19330051920276</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
         <v>123</v>
@@ -4235,13 +4075,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920150</v>
+        <v>19330051920151</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="D9" t="s">
         <v>124</v>
@@ -4252,13 +4092,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920153</v>
+        <v>19330051920157</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
         <v>125</v>
@@ -4269,13 +4109,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920152</v>
+        <v>19330051920160</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D11" t="s">
         <v>126</v>
@@ -4286,13 +4126,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920154</v>
+        <v>19330051920158</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D12" t="s">
         <v>127</v>
@@ -4303,13 +4143,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920276</v>
+        <v>19330051920159</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D13" t="s">
         <v>128</v>
@@ -4320,13 +4160,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920151</v>
+        <v>19330051920423</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="D14" t="s">
         <v>129</v>
@@ -4337,13 +4177,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920160</v>
+        <v>19330051920281</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="D15" t="s">
         <v>130</v>
@@ -4354,13 +4194,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920158</v>
+        <v>19330051920161</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D16" t="s">
         <v>131</v>
@@ -4371,13 +4211,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920159</v>
+        <v>19330051920162</v>
       </c>
       <c r="B17" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C17" t="s">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="D17" t="s">
         <v>132</v>
@@ -4388,13 +4228,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920423</v>
+        <v>19330051920155</v>
       </c>
       <c r="B18" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C18" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D18" t="s">
         <v>133</v>
@@ -4405,13 +4245,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920281</v>
+        <v>19330051920163</v>
       </c>
       <c r="B19" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D19" t="s">
         <v>134</v>
@@ -4422,13 +4262,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920161</v>
+        <v>19330051920156</v>
       </c>
       <c r="B20" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="C20" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="D20" t="s">
         <v>135</v>
@@ -4439,13 +4279,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920162</v>
+        <v>19330051920165</v>
       </c>
       <c r="B21" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D21" t="s">
         <v>136</v>
@@ -4456,16 +4296,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920163</v>
+        <v>19330051920166</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C22" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D22" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -4473,16 +4313,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920156</v>
+        <v>19330051920168</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="D23" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -4490,16 +4330,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920165</v>
+        <v>19330051920170</v>
       </c>
       <c r="B24" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C24" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="D24" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -4507,16 +4347,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920166</v>
+        <v>19330051920172</v>
       </c>
       <c r="B25" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="D25" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -4524,13 +4364,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920170</v>
+        <v>19330051920173</v>
       </c>
       <c r="B26" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C26" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="D26" t="s">
         <v>140</v>
@@ -4541,13 +4381,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920172</v>
+        <v>19330051920176</v>
       </c>
       <c r="B27" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="D27" t="s">
         <v>141</v>
@@ -4558,13 +4398,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920173</v>
+        <v>19330051920174</v>
       </c>
       <c r="B28" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D28" t="s">
         <v>142</v>
@@ -4575,13 +4415,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920176</v>
+        <v>19330051920175</v>
       </c>
       <c r="B29" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="D29" t="s">
         <v>143</v>
@@ -4592,13 +4432,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920174</v>
+        <v>19330051920178</v>
       </c>
       <c r="B30" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D30" t="s">
         <v>144</v>
@@ -4609,13 +4449,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>19330051920175</v>
+        <v>19330051920179</v>
       </c>
       <c r="B31" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C31" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="D31" t="s">
         <v>145</v>
@@ -4626,13 +4466,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>19330051920178</v>
+        <v>19330051920181</v>
       </c>
       <c r="B32" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C32" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D32" t="s">
         <v>146</v>
@@ -4643,13 +4483,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>19330051920179</v>
+        <v>19330051920180</v>
       </c>
       <c r="B33" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="C33" t="s">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="D33" t="s">
         <v>147</v>
@@ -4660,13 +4500,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>19330051920180</v>
+        <v>19330051920303</v>
       </c>
       <c r="B34" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="C34" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D34" t="s">
         <v>148</v>
@@ -4677,13 +4517,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>19330051920303</v>
+        <v>19330051920182</v>
       </c>
       <c r="B35" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="C35" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D35" t="s">
         <v>149</v>
@@ -4694,13 +4534,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>19330051920182</v>
+        <v>19330051920183</v>
       </c>
       <c r="B36" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C36" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D36" t="s">
         <v>150</v>
@@ -4716,7 +4556,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4748,19 +4588,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920151</v>
+        <v>19330051920155</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="D2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
         <v>57</v>
@@ -4771,22 +4611,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920151</v>
+        <v>19330051920155</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="D3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4794,22 +4634,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920159</v>
+        <v>19330051920181</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>112</v>
       </c>
       <c r="D4" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4817,24 +4657,70 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920165</v>
+        <v>19330051920181</v>
       </c>
       <c r="B5" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D5" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="E5" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
         <v>56</v>
       </c>
       <c r="G5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>19330051920151</v>
+      </c>
+      <c r="B6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D6" t="s">
+        <v>124</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>56</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>19330051920168</v>
+      </c>
+      <c r="B7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D7" t="s">
+        <v>137</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>56</v>
+      </c>
+      <c r="G7">
         <v>5</v>
       </c>
     </row>
